--- a/frontend/public/templates/students_template.xlsx
+++ b/frontend/public/templates/students_template.xlsx
@@ -455,14 +455,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>telegram</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Имя</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Телеграм</t>
         </is>
       </c>
     </row>
